--- a/output/graficos_regionales_indicadores/plot_regional_o_ocup_a_2023_los_lagos.xlsx
+++ b/output/graficos_regionales_indicadores/plot_regional_o_ocup_a_2023_los_lagos.xlsx
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 18:14</t>
+    <t xml:space="preserve">2026-09-09 19:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_indicadores/plot_regional_o_ocup_a_2023_los_lagos.xlsx
+++ b/output/graficos_regionales_indicadores/plot_regional_o_ocup_a_2023_los_lagos.xlsx
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 19:03</t>
+    <t xml:space="preserve">2026-09-18 09:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_indicadores/plot_regional_o_ocup_a_2023_los_lagos.xlsx
+++ b/output/graficos_regionales_indicadores/plot_regional_o_ocup_a_2023_los_lagos.xlsx
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 09:12</t>
+    <t xml:space="preserve">2026-10-05 06:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
